--- a/data/s0/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s0/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Kanaleneiland\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6856223F-62AC-40F4-A262-0A110E50AA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08BA4A5-ACEF-4B77-9A93-622683085876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -205,12 +208,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -225,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -233,6 +242,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,7 +564,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -594,7 +606,7 @@
       <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>43</v>
       </c>
       <c r="R1" t="s">
@@ -657,8 +669,8 @@
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>0.29944907087005901</v>
+      <c r="C2" s="7">
+        <v>5265</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -699,8 +711,9 @@
       <c r="P2">
         <v>240</v>
       </c>
-      <c r="Q2" s="3">
-        <v>0.30000000000000004</v>
+      <c r="Q2" s="8">
+        <f>1-0.66</f>
+        <v>0.33999999999999997</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -761,8 +774,8 @@
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>0.28136043946110434</v>
+      <c r="C3" s="7">
+        <v>5079</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -803,8 +816,9 @@
       <c r="P3">
         <v>240</v>
       </c>
-      <c r="Q3" s="3">
-        <v>0.35</v>
+      <c r="Q3" s="8">
+        <f>1-0.66</f>
+        <v>0.33999999999999997</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -865,8 +879,8 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
-        <v>0.16444947636569487</v>
+      <c r="C4" s="7">
+        <v>2675</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -907,7 +921,7 @@
       <c r="P4">
         <v>360</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
       <c r="R4">
@@ -969,8 +983,8 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
-        <v>7.1327483724879709E-2</v>
+      <c r="C5" s="7">
+        <v>1340</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -1011,7 +1025,7 @@
       <c r="P5">
         <v>240</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="9">
         <v>0.85</v>
       </c>
       <c r="R5">
@@ -1073,8 +1087,8 @@
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>0.1834135295782621</v>
+      <c r="C6" s="7">
+        <v>3210</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -1115,8 +1129,9 @@
       <c r="P6">
         <v>240</v>
       </c>
-      <c r="Q6" s="3">
-        <v>0.26</v>
+      <c r="Q6" s="8">
+        <f>1-0.66</f>
+        <v>0.33999999999999997</v>
       </c>
       <c r="R6">
         <v>0</v>
